--- a/output/pdf_financials_xlsx/FP.xlsx
+++ b/output/pdf_financials_xlsx/FP.xlsx
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7.171</v>
+        <v>7.131</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>7.222</v>
+        <v>7.071</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-7.34</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7.171</v>
+        <v>7.131</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>7.222</v>
+        <v>7.071</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-7.34</v>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>6.297919429489826</v>
+        <v>6.262789492635886</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>6.563545150501672</v>
+        <v>6.426312345499491</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E313" s="5" t="n">
@@ -35849,7 +35849,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E314" s="5" t="n">

--- a/output/pdf_financials_xlsx/FP.xlsx
+++ b/output/pdf_financials_xlsx/FP.xlsx
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.728</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.708</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7.131</v>
+        <v>7.859</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>7.071</v>
+        <v>7.779</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-7.34</v>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>6.262789492635886</v>
+        <v>6.902154343377568</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>6.426312345499491</v>
+        <v>7.069761523920313</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -35586,14 +35586,14 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E311" s="5" t="n">
-        <v>-0.728</v>
+        <v>0.728</v>
       </c>
       <c r="F311" s="5" t="n">
-        <v>-0.708</v>
+        <v>0.708</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FP.xlsx
+++ b/output/pdf_financials_xlsx/FP.xlsx
@@ -1358,10 +1358,10 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.631</v>
+        <v>-0.631</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-2.06</v>
+        <v>2.06</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>3.462</v>
@@ -1396,10 +1396,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N17" s="3" t="n">
+        <v>-0.042</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-0.655</v>
@@ -3581,34 +3579,34 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>70.661</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>74.571</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>71.25</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>74.596</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>79.64700000000001</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>79.792</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>79.878</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>79.771</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>79.744</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>79.792</v>
       </c>
       <c r="M56" s="3" t="n">
         <v>0</v>
@@ -3633,34 +3631,34 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>32.794</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>34.07</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>6.586</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>39.779</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>43.614</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>46.904</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>50.544</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>53.19</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>55.627</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>58.081</v>
       </c>
       <c r="M57" s="3" t="n">
         <v>0</v>
@@ -3688,16 +3686,16 @@
         <v>37.867</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0</v>
+        <v>40.501</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0</v>
+        <v>64.664</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0</v>
+        <v>34.817</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0</v>
+        <v>36.033</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>32.888</v>
@@ -3706,13 +3704,13 @@
         <v>29.334</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0</v>
+        <v>26.581</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0</v>
+        <v>24.117</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0</v>
+        <v>21.711</v>
       </c>
       <c r="M58" s="3" t="n">
         <v>0</v>
@@ -3844,16 +3842,16 @@
         <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>45.191</v>
+        <v>4.69</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>45.251</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>44.892</v>
+        <v>10.075</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>43.14</v>
+        <v>7.107</v>
       </c>
       <c r="H61" s="3" t="n">
         <v>0</v>
@@ -3862,13 +3860,13 @@
         <v>0</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>6.411</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>4.808</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>5.617</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3" t="n">
         <v>8.327999999999999</v>
@@ -19718,7 +19716,11 @@
           <t>Deferred income tax expense 7</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -22997,7 +22999,11 @@
           <t>Deferred income tax expense (recovery) 8</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -23608,7 +23614,11 @@
           <t>Deferred income tax expense (recovery) 8</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -24611,7 +24621,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -25600,7 +25614,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E201" s="5" t="n">
         <v>0.05</v>
       </c>
@@ -27693,7 +27711,11 @@
           <t>Current income tax recovery 7</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -27782,7 +27804,11 @@
           <t>Deferred income tax recovery 7</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -28957,7 +28983,11 @@
           <t>Deferred income tax recovery (expense) 7</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -29873,7 +29903,11 @@
           <t>Deferred income tax recovery 8</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -32694,7 +32728,11 @@
           <t>Deferred income tax recovery (expense) 8</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -32965,7 +33003,11 @@
           <t>Deferred income tax recovery 8</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -33792,7 +33834,11 @@
           <t>Deferred income tax recovery (expense) 9</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -34063,7 +34109,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -35064,7 +35114,11 @@
           <t>Net earnings (loss) -</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
